--- a/classification/icd1011.xlsx
+++ b/classification/icd1011.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jator\Documents\GitHub\data\disease_outbreak_news\disease_outbreak_news\classification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0963D286-CE91-4B94-B5ED-BD441D31FCE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2BDE04-E821-40BB-BB3D-D6B5CEC6EF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="676">
   <si>
     <t>icd10c</t>
   </si>
@@ -2044,6 +2044,27 @@
   </si>
   <si>
     <t>Ebola disease caused by Sudan virus.</t>
+  </si>
+  <si>
+    <t>Pneumonia, unspecified</t>
+  </si>
+  <si>
+    <t>J189</t>
+  </si>
+  <si>
+    <t>J18</t>
+  </si>
+  <si>
+    <t>Pneumonia, organism unspecified</t>
+  </si>
+  <si>
+    <t>A disease of the lungs, frequently but not always caused by an infection with bacteria, virus, fungus, or parasite. This disease is characterised by fever, chills, cough with sputum production, chest pain and shortness of breath. Confirmation is, for example, by chest x-ray.</t>
+  </si>
+  <si>
+    <t>CA40Z</t>
+  </si>
+  <si>
+    <t>12CA40Z</t>
   </si>
 </sst>
 </file>
@@ -2432,7 +2453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N92"/>
+  <dimension ref="A1:N93"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
@@ -6453,6 +6474,50 @@
         <v>668</v>
       </c>
     </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>488</v>
+      </c>
+      <c r="B93" t="s">
+        <v>671</v>
+      </c>
+      <c r="C93" t="s">
+        <v>670</v>
+      </c>
+      <c r="D93" t="s">
+        <v>491</v>
+      </c>
+      <c r="E93" t="s">
+        <v>672</v>
+      </c>
+      <c r="F93" t="s">
+        <v>669</v>
+      </c>
+      <c r="G93">
+        <v>12</v>
+      </c>
+      <c r="H93" t="s">
+        <v>674</v>
+      </c>
+      <c r="I93" t="s">
+        <v>675</v>
+      </c>
+      <c r="J93" t="s">
+        <v>503</v>
+      </c>
+      <c r="K93" t="s">
+        <v>504</v>
+      </c>
+      <c r="L93" t="s">
+        <v>505</v>
+      </c>
+      <c r="M93" t="s">
+        <v>672</v>
+      </c>
+      <c r="N93" t="s">
+        <v>673</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N92" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
